--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="228">
   <si>
     <t>pathway</t>
   </si>
@@ -40,13 +40,13 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E2398,E1116,E1164,E2356,E2457,E1118,E2669,E2141,E2504,E2671,E2142,E2274,E1037,E2275,E2394,E1691,E1163,E1950,E1954,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C05487/C05475/C05478,C05476,C05472,C05488/C05497/C05477/C02140,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C00410,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,CE1352,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Progesterone; 4-Pregnene-3,20-dione$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha-hydroxypregnenolone sulfate$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+    <t>E2263,E2398,E1116,E2356,E2457,E1118,E2669,E1164,E2141,E2504,E2671,E2142,E2274,E1037,E2275,E2394,E1691,E1163,E1950,E1954,E1955,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C05476,C05472,C05488/C05497/C05477/C02140,C05489/C05471/C05474,C05487/C05475/C05478,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C00410,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,CE1352,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Progesterone; 4-Pregnene-3,20-dione$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha-hydroxypregnenolone sulfate$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
   </si>
   <si>
     <t>Linoleate metabolism</t>
@@ -91,10 +91,10 @@
     <t>E2779,E2775</t>
   </si>
   <si>
-    <t>CE0955/CE6232/CE5945,CE0955/CE6232/CE5945</t>
-  </si>
-  <si>
-    <t>/prostaglandin G1/10,11-dihydro-20-dihydroxy-LTB4$/prostaglandin G1/10,11-dihydro-20-dihydroxy-LTB4</t>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
   </si>
   <si>
     <t>Leukotriene metabolism</t>
@@ -103,10 +103,10 @@
     <t>E2298,E975,E1900,E1286,E2775,E1302,E2297,E1017,E1899,E2779,E1820,E1822,E2295</t>
   </si>
   <si>
-    <t>,,,,CE0955/CE6232/CE5945,,,,,CE0955/CE6232/CE5945,,,</t>
-  </si>
-  <si>
-    <t>$$$$/prostaglandin G1/10,11-dihydro-20-dihydroxy-LTB4$$$$$/prostaglandin G1/10,11-dihydro-20-dihydroxy-LTB4$$$</t>
+    <t>,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$</t>
   </si>
   <si>
     <t>Limonene and pinene degradation</t>
@@ -181,10 +181,10 @@
     <t>E975,E2775,E1331,E3067,E1017,E1647,E2779,E969,E1760</t>
   </si>
   <si>
-    <t>,CE0955/CE6232/CE5945,,,,,CE0955/CE6232/CE5945,,</t>
-  </si>
-  <si>
-    <t>$/prostaglandin G1/10,11-dihydro-20-dihydroxy-LTB4$$$$$/prostaglandin G1/10,11-dihydro-20-dihydroxy-LTB4$$</t>
+    <t>,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$</t>
   </si>
   <si>
     <t>Glycerophospholipid metabolism</t>
@@ -233,12 +233,6 @@
   </si>
   <si>
     <t>E1587,E1403</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
   </si>
   <si>
     <t>Putative anti-Inflammatory metabolites formation from EPA</t>
@@ -1072,7 +1066,7 @@
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.01216786272499622</v>
+        <v>0.01310902337775836</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1095,7 +1089,7 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>0.0169072788692627</v>
+        <v>0.0176299557990622</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1118,7 +1112,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0.02378111292247189</v>
+        <v>0.02507520882001983</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1141,7 +1135,7 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>0.0349237827935665</v>
+        <v>0.03682291053931867</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1164,7 +1158,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.04961261155274702</v>
+        <v>0.05159577149963866</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1187,7 +1181,7 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>0.06917530797801717</v>
+        <v>0.0734105309154468</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1210,7 +1204,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.07606594847145426</v>
+        <v>0.0795280751584007</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1233,7 +1227,7 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>0.07976336532159123</v>
+        <v>0.08325910488899346</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1256,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>0.08470445874859246</v>
+        <v>0.08756155358733467</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1279,7 +1273,7 @@
         <v>18</v>
       </c>
       <c r="D11">
-        <v>0.1082838943883296</v>
+        <v>0.113040116972824</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1302,7 +1296,7 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>0.1090906035192686</v>
+        <v>0.113678761701484</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1325,7 +1319,7 @@
         <v>11</v>
       </c>
       <c r="D13">
-        <v>0.1100821834927144</v>
+        <v>0.1146031159140183</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1348,7 +1342,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>0.1103678929765886</v>
+        <v>0.1152753735231341</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
@@ -1371,7 +1365,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>0.1365859397321053</v>
+        <v>0.1408715819902187</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -1394,7 +1388,7 @@
         <v>120</v>
       </c>
       <c r="D16">
-        <v>0.1414261945177392</v>
+        <v>0.1461488042217778</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -1417,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1622493739601015</v>
+        <v>0.1655770491252248</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1440,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>0.1950051259642695</v>
+        <v>0.1972403825145796</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
@@ -1463,21 +1457,21 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>0.1950051259642695</v>
+        <v>0.1972403825145796</v>
       </c>
       <c r="E19" t="s">
         <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1486,21 +1480,21 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>0.2502478949933615</v>
+        <v>0.2501806692324499</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -1509,21 +1503,21 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>0.2502478949933615</v>
+        <v>0.2501806692324499</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1532,15 +1526,15 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>0.2668358514982941</v>
+        <v>0.2664997226937362</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1549,15 +1543,15 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>0.2668358514982941</v>
+        <v>0.2664997226937362</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -1569,18 +1563,18 @@
         <v>0.3129863363640947</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -1589,21 +1583,21 @@
         <v>22</v>
       </c>
       <c r="D25">
-        <v>0.3377422228197846</v>
+        <v>0.3360783852372229</v>
       </c>
       <c r="E25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" t="s">
         <v>85</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -1612,21 +1606,21 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>0.349221021495437</v>
+        <v>0.3474899581519638</v>
       </c>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -1635,21 +1629,21 @@
         <v>9</v>
       </c>
       <c r="D27">
-        <v>0.349221021495437</v>
+        <v>0.3474899581519638</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1658,10 +1652,10 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>0.3874220601334432</v>
+        <v>0.3851195778222214</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
         <v>69</v>
@@ -1672,7 +1666,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1681,15 +1675,15 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>0.3911026705433522</v>
+        <v>0.3898253810860322</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1698,15 +1692,15 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>0.3911026705433522</v>
+        <v>0.3898253810860322</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1715,15 +1709,15 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>0.3911026705433522</v>
+        <v>0.3898253810860322</v>
       </c>
       <c r="E31" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B32">
         <v>35</v>
@@ -1732,21 +1726,21 @@
         <v>152</v>
       </c>
       <c r="D32">
-        <v>0.398531117124082</v>
+        <v>0.3977916337540546</v>
       </c>
       <c r="E32" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" t="s">
         <v>101</v>
-      </c>
-      <c r="F32" t="s">
-        <v>102</v>
-      </c>
-      <c r="G32" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1755,21 +1749,21 @@
         <v>11</v>
       </c>
       <c r="D33">
-        <v>0.428228097006773</v>
+        <v>0.4262449370598814</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -1778,15 +1772,15 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>0.4433370867716509</v>
+        <v>0.4416564427488613</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1795,15 +1789,15 @@
         <v>6</v>
       </c>
       <c r="D35">
-        <v>0.4433370867716509</v>
+        <v>0.4416564427488613</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1812,15 +1806,15 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>0.4433370867716509</v>
+        <v>0.4416564427488613</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B37">
         <v>3</v>
@@ -1829,21 +1823,21 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0.4599922690374952</v>
+        <v>0.4575385287642225</v>
       </c>
       <c r="E37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" t="s">
         <v>112</v>
-      </c>
-      <c r="F37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G37" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -1852,10 +1846,10 @@
         <v>17</v>
       </c>
       <c r="D38">
-        <v>0.4599922690374952</v>
+        <v>0.4575385287642225</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F38" t="s">
         <v>41</v>
@@ -1866,7 +1860,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -1875,21 +1869,21 @@
         <v>12</v>
       </c>
       <c r="D39">
-        <v>0.4635888472462648</v>
+        <v>0.4611519134132199</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -1898,21 +1892,21 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>0.4664459420850069</v>
+        <v>0.4642779112956085</v>
       </c>
       <c r="E40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -1921,21 +1915,21 @@
         <v>51</v>
       </c>
       <c r="D41">
-        <v>0.4832355758726744</v>
+        <v>0.4807482227189459</v>
       </c>
       <c r="E41" t="s">
+        <v>120</v>
+      </c>
+      <c r="F41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G41" t="s">
         <v>122</v>
-      </c>
-      <c r="F41" t="s">
-        <v>123</v>
-      </c>
-      <c r="G41" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1944,15 +1938,15 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4860758642711887</v>
+        <v>0.4831683501117628</v>
       </c>
       <c r="E42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1961,15 +1955,15 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4860758642711887</v>
+        <v>0.4831683501117628</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1978,15 +1972,15 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>0.4860758642711887</v>
+        <v>0.4831683501117628</v>
       </c>
       <c r="E44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -1995,21 +1989,21 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>0.4860758642711887</v>
+        <v>0.4831683501117628</v>
       </c>
       <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" t="s">
         <v>130</v>
-      </c>
-      <c r="F45" t="s">
-        <v>131</v>
-      </c>
-      <c r="G45" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B46">
         <v>2</v>
@@ -2018,21 +2012,21 @@
         <v>13</v>
       </c>
       <c r="D46">
-        <v>0.4930337305255374</v>
+        <v>0.4907480546545436</v>
       </c>
       <c r="E46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B47">
         <v>8</v>
@@ -2041,21 +2035,21 @@
         <v>43</v>
       </c>
       <c r="D47">
-        <v>0.5019075309658662</v>
+        <v>0.4990840490075797</v>
       </c>
       <c r="E47" t="s">
+        <v>133</v>
+      </c>
+      <c r="F47" t="s">
+        <v>134</v>
+      </c>
+      <c r="G47" t="s">
         <v>135</v>
-      </c>
-      <c r="F47" t="s">
-        <v>136</v>
-      </c>
-      <c r="G47" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2064,21 +2058,21 @@
         <v>8</v>
       </c>
       <c r="D48">
-        <v>0.5163610695618561</v>
+        <v>0.5140585872506345</v>
       </c>
       <c r="E48" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" t="s">
         <v>139</v>
-      </c>
-      <c r="F48" t="s">
-        <v>140</v>
-      </c>
-      <c r="G48" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B49">
         <v>2</v>
@@ -2087,21 +2081,21 @@
         <v>14</v>
       </c>
       <c r="D49">
-        <v>0.5165963597250466</v>
+        <v>0.5144619418161039</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B50">
         <v>2</v>
@@ -2110,21 +2104,21 @@
         <v>14</v>
       </c>
       <c r="D50">
-        <v>0.5165963597250466</v>
+        <v>0.5144619418161039</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F50" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -2133,15 +2127,15 @@
         <v>9</v>
       </c>
       <c r="D51">
-        <v>0.5378228937328784</v>
+        <v>0.5355036049814289</v>
       </c>
       <c r="E51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -2150,15 +2144,15 @@
         <v>9</v>
       </c>
       <c r="D52">
-        <v>0.5378228937328784</v>
+        <v>0.5355036049814289</v>
       </c>
       <c r="E52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -2167,15 +2161,15 @@
         <v>10</v>
       </c>
       <c r="D53">
-        <v>0.5556713332549033</v>
+        <v>0.5523268516495521</v>
       </c>
       <c r="E53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -2184,15 +2178,15 @@
         <v>10</v>
       </c>
       <c r="D54">
-        <v>0.5556713332549033</v>
+        <v>0.5523268516495521</v>
       </c>
       <c r="E54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -2201,15 +2195,15 @@
         <v>10</v>
       </c>
       <c r="D55">
-        <v>0.5556713332549033</v>
+        <v>0.5523268516495521</v>
       </c>
       <c r="E55" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -2218,15 +2212,15 @@
         <v>10</v>
       </c>
       <c r="D56">
-        <v>0.5556713332549033</v>
+        <v>0.5523268516495521</v>
       </c>
       <c r="E56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2235,15 +2229,15 @@
         <v>11</v>
       </c>
       <c r="D57">
-        <v>0.5715198063898086</v>
+        <v>0.5695702593233727</v>
       </c>
       <c r="E57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -2252,21 +2246,21 @@
         <v>18</v>
       </c>
       <c r="D58">
-        <v>0.5760071259306566</v>
+        <v>0.5739231273423976</v>
       </c>
       <c r="E58" t="s">
+        <v>155</v>
+      </c>
+      <c r="F58" t="s">
+        <v>156</v>
+      </c>
+      <c r="G58" t="s">
         <v>157</v>
-      </c>
-      <c r="F58" t="s">
-        <v>158</v>
-      </c>
-      <c r="G58" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -2275,15 +2269,15 @@
         <v>12</v>
       </c>
       <c r="D59">
-        <v>0.5832507016688795</v>
+        <v>0.580763348515151</v>
       </c>
       <c r="E59" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2292,15 +2286,15 @@
         <v>14</v>
       </c>
       <c r="D60">
-        <v>0.5945278230617973</v>
+        <v>0.5925278566746778</v>
       </c>
       <c r="E60" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -2309,21 +2303,21 @@
         <v>14</v>
       </c>
       <c r="D61">
-        <v>0.5945278230617973</v>
+        <v>0.5925278566746778</v>
       </c>
       <c r="E61" t="s">
+        <v>163</v>
+      </c>
+      <c r="F61" t="s">
+        <v>164</v>
+      </c>
+      <c r="G61" t="s">
         <v>165</v>
-      </c>
-      <c r="F61" t="s">
-        <v>166</v>
-      </c>
-      <c r="G61" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -2332,15 +2326,15 @@
         <v>15</v>
       </c>
       <c r="D62">
-        <v>0.5990151426026453</v>
+        <v>0.5973008856994</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -2349,15 +2343,15 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>0.6049814288835482</v>
+        <v>0.603569687904405</v>
       </c>
       <c r="E63" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -2366,21 +2360,21 @@
         <v>35</v>
       </c>
       <c r="D64">
-        <v>0.6113846826103763</v>
+        <v>0.6099225223105494</v>
       </c>
       <c r="E64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F64" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" t="s">
         <v>171</v>
-      </c>
-      <c r="F64" t="s">
-        <v>172</v>
-      </c>
-      <c r="G64" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2389,12 +2383,12 @@
         <v>6</v>
       </c>
       <c r="D65">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2403,12 +2397,12 @@
         <v>8</v>
       </c>
       <c r="D66">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2417,12 +2411,12 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2431,12 +2425,12 @@
         <v>2</v>
       </c>
       <c r="D68">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2445,12 +2439,12 @@
         <v>1</v>
       </c>
       <c r="D69">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2459,12 +2453,12 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2473,12 +2467,12 @@
         <v>4</v>
       </c>
       <c r="D71">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2487,12 +2481,12 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2501,12 +2495,12 @@
         <v>5</v>
       </c>
       <c r="D73">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2515,12 +2509,12 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2529,12 +2523,12 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2543,12 +2537,12 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2557,12 +2551,12 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2571,12 +2565,12 @@
         <v>3</v>
       </c>
       <c r="D78">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2585,12 +2579,12 @@
         <v>5</v>
       </c>
       <c r="D79">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2599,12 +2593,12 @@
         <v>14</v>
       </c>
       <c r="D80">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2613,12 +2607,12 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2627,12 +2621,12 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2641,12 +2635,12 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2655,12 +2649,12 @@
         <v>2</v>
       </c>
       <c r="D84">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2669,12 +2663,12 @@
         <v>4</v>
       </c>
       <c r="D85">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2683,12 +2677,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2697,12 +2691,12 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2711,12 +2705,12 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2725,12 +2719,12 @@
         <v>2</v>
       </c>
       <c r="D89">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2739,12 +2733,12 @@
         <v>3</v>
       </c>
       <c r="D90">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2753,12 +2747,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2767,12 +2761,12 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2781,12 +2775,12 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2795,12 +2789,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2809,12 +2803,12 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2823,12 +2817,12 @@
         <v>2</v>
       </c>
       <c r="D96">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2837,12 +2831,12 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2851,12 +2845,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2865,12 +2859,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2879,12 +2873,12 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2893,12 +2887,12 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2907,12 +2901,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2921,12 +2915,12 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2935,12 +2929,12 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2949,12 +2943,12 @@
         <v>6</v>
       </c>
       <c r="D105">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2963,12 +2957,12 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2977,12 +2971,12 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2991,12 +2985,12 @@
         <v>3</v>
       </c>
       <c r="D108">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3005,12 +2999,12 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3019,12 +3013,12 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3033,12 +3027,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3047,12 +3041,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3061,12 +3055,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3075,12 +3069,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3089,12 +3083,12 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3103,12 +3097,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3117,12 +3111,12 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3131,12 +3125,12 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3145,12 +3139,12 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3159,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.6123594561435942</v>
+        <v>0.6111493924471858</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="228">
   <si>
     <t>pathway</t>
   </si>
@@ -40,115 +40,280 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E2398,E1116,E2356,E2457,E1118,E2669,E1164,E2141,E2504,E2671,E2142,E2274,E1037,E2275,E2394,E1691,E1163,E1950,E1954,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C05476,C05472,C05488/C05497/C05477/C02140,C05489/C05471/C05474,C05487/C05475/C05478,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C00410,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,CE1352,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Progesterone; 4-Pregnene-3,20-dione$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha-hydroxypregnenolone sulfate$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E1164,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1950,E1954,E1951,E1955,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C05487/C05475/C05478,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E909,E912,E1455,E1439,E290,E908,E288,E291</t>
+  </si>
+  <si>
+    <t>C00079/CE2172,C00079/CE2172,CE2705/CE5236,C00268/C02953/C04244,C00082/CE2174,C00079/CE2172,C00082/CE2174,C00082/CE2174</t>
+  </si>
+  <si>
+    <t>L-Phenylalanine/$L-Phenylalanine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Tyrosine/$L-Phenylalanine/$L-Tyrosine/$L-Tyrosine/</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E179,E796,E1684,E522,E1274,E2919,E2447,E800,E803,E794,E2336,E178,E801,E940</t>
+  </si>
+  <si>
+    <t>C16586/CE2173,C05635/C16596,C16602/C16601/C07496,C16595/C16587,C16582/C16584,C07108,C16608,C16591,C16591,C05635/C16596,C16609,C16586/CE2173,C16591,C07501</t>
+  </si>
+  <si>
+    <t>2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$3-Hydroxycarbamazepine/2-Hydroxycarbamazepine/Carbamazepine-10,11-epoxide; Carbamazepine epoxide$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$2-Hydroxyfelbamate/p-Hydroxyfelbamate$Tamoxifen$Demethylcitalopram$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$Didemethylcitalopram$2-Phenyl-1,3-propanediol monocarbamate/$3-Carbamoyl-2-phenylpropionic acid$Felbamate</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E2298,E1015,E92,E975,E2296,E2297,E1017,E2513,E2295</t>
+  </si>
+  <si>
+    <t>C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C06426/C06427,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C00909,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00909</t>
+  </si>
+  <si>
+    <t>Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$Leukotriene A4$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Leukotriene A4</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E1036,E556,E1176,E422,E2141,E2266,E1950,E1037,E2153,E1954,E2142,E1951,E2394,E1955,E2149</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,C04042/C01953/C03681,CE2209,C02538,dhea/C03772/C01227/C00674/C00535,C03917/C05293/C00523/C04373/C04295,andrstndn/C00280,C11134/tststeroneglc,C04042/C01953/C03681,CE2186/CE2183/C05302/C05284/C05290/C05140,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C03917/C05293/C00523/C04373/C04295,C11134/tststeroneglc,C18038/C05138/C04518/C05485,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,CE5256/CE5251/CE5252/CE5255</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$5alpha-androstane-3alpha,17beta-diol$Estrone 3-sulfate$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$estrone-2,3-semiquinone/estrone-3,4-quinone/estrone-2,3-quinone/estrone-3,4-semiquinone</t>
+  </si>
+  <si>
+    <t>Pentose and Glucuronate Interconversions</t>
+  </si>
+  <si>
+    <t>E47,E48</t>
+  </si>
+  <si>
+    <t>C00257/C00800,C00259/C00309/C00312/C00310/C00121/C00181</t>
+  </si>
+  <si>
+    <t>D-Gluconate/L-Gulonate$L-Arabinose/D-Ribulose; D-erythro-2-Pentulose; D-Arabinoketose; D-Arabinulose; D-Riboketose/L-Xylulose/D-Xylulose/D-Ribose/D-Xylose</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E2325,E92,E2326</t>
+  </si>
+  <si>
+    <t>C16300,C06426/C06427,C16300</t>
+  </si>
+  <si>
+    <t>Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E2191,E1107,E1113</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>$$</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E1015,E975,E1331,E3067,E1017,E1647,E2779,E969,E1760</t>
+  </si>
+  <si>
+    <t>C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,,,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,,,</t>
+  </si>
+  <si>
+    <t>5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$$$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$$$</t>
+  </si>
+  <si>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>E48</t>
+  </si>
+  <si>
+    <t>C00259/C00309/C00312/C00310/C00121/C00181</t>
+  </si>
+  <si>
+    <t>L-Arabinose/D-Ribulose; D-erythro-2-Pentulose; D-Arabinoketose; D-Arabinulose; D-Riboketose/L-Xylulose/D-Xylulose/D-Ribose/D-Xylose</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E86,E2286,E2485,E3147,E2166,E2513</t>
+  </si>
+  <si>
+    <t>,,,,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>$$$$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
   </si>
   <si>
     <t>Linoleate metabolism</t>
   </si>
   <si>
-    <t>E92,E2348,E113,E2350,E480,E947,E2321,E492,E114,E948,E250,E112,E479,E2782</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C14762/C14826/C14825,CE2061,C14762/C14826/C14825,CE2006/CE6506,CE5528,CE5526/CE5527/C14765,C04717/C14827,CE2061,CE5528,C08261,CE2061,CE2006/CE6506,CE6415/CE6502</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$/$$//13-OxoODE; 13-KODE; (9Z,11E)-13-Oxooctadeca-9,11-dienoic acid$(9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoic acid; (9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoate; 13(S)-HPODE; 13S-Hydroperoxy-9Z,11E-octadecadienoic acid/9(S)-HPODE; 9(S)-HPOD; (10E,12Z)-(9S)-9-Hydroperoxyoctadeca-10,12-dienoic acid$$$$$/$/</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E912,E1459,E1455,E290,E906,E908,E288,E291</t>
-  </si>
-  <si>
-    <t>C00079/CE2172,CE2705/CE5236,CE2705/CE5236,C00082/CE2174,C03684/C00835,C00079/CE2172,C00082/CE2174,C00082/CE2174</t>
-  </si>
-  <si>
-    <t>L-Phenylalanine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$L-Tyrosine/$6-Pyruvoyl-5,6,7,8-tetrahydropterin/Sepiapterin$L-Phenylalanine/$L-Tyrosine/$L-Tyrosine/</t>
+    <t>E92,E2350,E2738,E480,E947,E2321,E492,E2349,E2084,E250,E479</t>
+  </si>
+  <si>
+    <t>C06426/C06427,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E2298,E1015,E975,E1286,E2296,E1302,E2297,E1017,E1899,E2779,E1820,E2295</t>
+  </si>
+  <si>
+    <t>C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,,C00909,,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,,,C00909</t>
+  </si>
+  <si>
+    <t>Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$$Leukotriene A4$$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$$$Leukotriene A4</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>E2191,E1107,E725,E1113</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
   </si>
   <si>
     <t>Vitamin B9 (folate) metabolism</t>
   </si>
   <si>
-    <t>E1823,E1897,E506,E2050,E582</t>
-  </si>
-  <si>
-    <t>C00504,C00445,C01045/C01042,C00921,C00234/C03479</t>
-  </si>
-  <si>
-    <t>Folate$5,10-Methenyltetrahydrofolate$N-Formyl-L-glutamate/N-Acetyl-L-aspartate$Dihydropteroate; 7,8-Dihydropteroate$10-Formyltetrahydrofolate/5-Formyltetrahydrofolate</t>
+    <t>E1823,E1897,E2050,E2049</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E2511,E1520,E2728,E354</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E262,E94,E93</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E1350,E92,E2383,E2986,E1349,E2985,E2513</t>
+  </si>
+  <si>
+    <t>,C06426/C06427,,,,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E975,E2550</t>
+  </si>
+  <si>
+    <t>CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,</t>
+  </si>
+  <si>
+    <t>5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>E1202,E1197</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E33,E48</t>
+  </si>
+  <si>
+    <t>,C00259/C00309/C00312/C00310/C00121/C00181</t>
+  </si>
+  <si>
+    <t>$L-Arabinose/D-Ribulose; D-erythro-2-Pentulose; D-Arabinoketose; D-Arabinulose; D-Riboketose/L-Xylulose/D-Xylulose/D-Ribose/D-Xylose</t>
   </si>
   <si>
     <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
   </si>
   <si>
-    <t>E2779,E2775</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E2298,E975,E1900,E1286,E2775,E1302,E2297,E1017,E1899,E2779,E1820,E1822,E2295</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E99,E257,E263,E262</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E2298,E975,E92,E2773,E1017,E2297,E2513,E2295</t>
-  </si>
-  <si>
-    <t>,,C06426/C06427,,,,,</t>
-  </si>
-  <si>
-    <t>$$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$$$</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E2191,E1107,E1113</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E86,E2286,E2485,E3147,E2166,E2513</t>
+    <t>E2779</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E3036,E1371</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E1353,E1475,E1474,E1074</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E287,E1222,E22,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E283,E833,E66,E410,E170</t>
+  </si>
+  <si>
+    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,C03758,,C00822/C05604,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C03758,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$Dopamine$$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$Dopamine$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E1129,E1119,E2745,E2859,E1128,E3153</t>
   </si>
   <si>
     <t>,,,,,</t>
@@ -157,529 +322,364 @@
     <t>$$$$$</t>
   </si>
   <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E179,E796,E1684,E522,E2256,E1274,E2919,E2447,E803,E2336,E178,E801</t>
-  </si>
-  <si>
-    <t>C16586/CE2173,C16596,,C16595/C16587,,,,C16608,C16591,C16609,C16586/CE2173,C16591</t>
-  </si>
-  <si>
-    <t>2-Phenyl-1,3-propanediol monocarbamate/$5-Phenyl-1,3-oxazinane-2,4-dione$$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$$Demethylcitalopram$3-Carbamoyl-2-phenylpropionic acid$Didemethylcitalopram$2-Phenyl-1,3-propanediol monocarbamate/$3-Carbamoyl-2-phenylpropionic acid</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>E2191,E1107,E725,E1113</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E975,E2775,E1331,E3067,E1017,E1647,E2779,E969,E1760</t>
-  </si>
-  <si>
-    <t>,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E1350,E92,E2383,E2986,E1349,E1351,E2985,E2513</t>
-  </si>
-  <si>
-    <t>,C06426/C06427,,,,,,</t>
-  </si>
-  <si>
-    <t>$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$$$$</t>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>E317,E315</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E1408,E2897</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E92,E2166</t>
+  </si>
+  <si>
+    <t>C06426/C06427,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E26,E411,E1634,E1528,E144,E1535,E1208,E410,E413</t>
+  </si>
+  <si>
+    <t>,C05589/C00788,,,CE5536,,,C05589/C00788,C05589/C00788</t>
+  </si>
+  <si>
+    <t>$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$$adrenochrome$$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>E1783</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>E2100,E2409</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>E1417</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E33</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E3074,E3075,E2173,E2940</t>
   </si>
   <si>
     <t>Tryptophan metabolism</t>
   </si>
   <si>
-    <t>E796,E823,E639,E666,E877,E1155,E123,E1438,E1167,E772,E879,E776,E597,E1168,E609,E598,E1186,E1138,E632,E763,E1187,E2747,E846,E738,E634,E588,E1151,E651,E705,E767,E2802,E2751</t>
-  </si>
-  <si>
-    <t>C16596,,C00637,C01598,CE5860,C00978,,C05642,,C00328/C05647,CE5860,C06212,C00780,,,C00780,C05643,C00643,,C05638,C05643,CE3140,C02406/C02700,,,C00078/C00525,C00978,,C01252,C00328/C05647,,CE3140</t>
-  </si>
-  <si>
-    <t>5-Phenyl-1,3-oxazinane-2,4-dione$$Indole-3-acetaldehyde$Melatonin; N-Acetyl-5-methoxytryptamine$$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$$Formyl-N-acetyl-5-methoxykynurenamine$$L-Kynurenine/Formyl-5-hydroxykynurenamine$$N-Methylserotonin$Serotonin$$$Serotonin$6-Hydroxymelatonin$5-Hydroxy-L-tryptophan$$5-Hydroxykynurenamine$6-Hydroxymelatonin$$Formylkynurenine/L-Formylkynurenine$$$L-Tryptophan/D-Tryptophan$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$$4-(2-Aminophenyl)-2,4-dioxobutanoate$L-Kynurenine/Formyl-5-hydroxykynurenamine$$</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E2511,E1520,E2728,E354</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2325</t>
-  </si>
-  <si>
-    <t>C06426/C06427,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1587,E1403</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E975,E2550</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>E1202,E1197</t>
+    <t>E796,E639,E877,E123,E1438,E124,E772,E879,E597,E609,E598,E1186,E610,E527,E1138,E632,E763,E1187,E738,E588,E651,E705,E1439,E767,E794</t>
+  </si>
+  <si>
+    <t>C05635/C16596,C00637,CE5860,,C05642,,C05647,CE5860,C00780,,C00780,,,C00954/C05634,C00643,CE1918,C05638,,CE2122,C00078/C00525,C05660,,C00268/C02953/C04244,C05647,C05635/C16596</t>
+  </si>
+  <si>
+    <t>5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$Indole-3-acetaldehyde$$$Formyl-N-acetyl-5-methoxykynurenamine$$Formyl-5-hydroxykynurenamine$$Serotonin$$Serotonin$$$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$5-Hydroxy-L-tryptophan$5-hydroxytryptophol$5-Hydroxykynurenamine$$methyl indole-3-acetate$L-Tryptophan/D-Tryptophan$5-Methoxyindoleacetate$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Formyl-5-hydroxykynurenamine$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>E2765</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E1488,E1403</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>E2383,E3164</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E92</t>
+  </si>
+  <si>
+    <t>C06426/C06427</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>E47,E860</t>
+  </si>
+  <si>
+    <t>C00257/C00800,</t>
+  </si>
+  <si>
+    <t>D-Gluconate/L-Gulonate$</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1044</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E2570</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E15</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E833</t>
+  </si>
+  <si>
+    <t>C02763/C00166</t>
+  </si>
+  <si>
+    <t>enol-Phenylpyruvate/Phenylpyruvate</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E1208,E48</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
   </si>
   <si>
     <t>Electron transport chain</t>
   </si>
   <si>
-    <t>E2089</t>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
   </si>
   <si>
     <t>Fatty acid oxidation</t>
   </si>
   <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E1372,E3036</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2173,E3074,E100,E2940,E2941</t>
-  </si>
-  <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E317,E315</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E1408,E2897</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E92,E2166</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>E742</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>E1783</t>
+    <t>ROS Detoxification</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Geraniol degradation</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Dynorphin metabolism</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation, peroxisome</t>
+  </si>
+  <si>
+    <t>Polyunsaturated fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Keratan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>3-Chloroacrylic acid degradation</t>
+  </si>
+  <si>
+    <t>Sphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>O-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Proteoglycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin K metabolism</t>
+  </si>
+  <si>
+    <t>Glutamate metabolism</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol phosphate metabolism</t>
+  </si>
+  <si>
+    <t>Benzoate degradation via CoA ligation</t>
+  </si>
+  <si>
+    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
+  </si>
+  <si>
+    <t>Atrazine degradation</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>Carbon fixation</t>
+  </si>
+  <si>
+    <t>Nucleotide Sugar Metabolism</t>
+  </si>
+  <si>
+    <t>1- and 2-Methylnaphthalene degradation</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>Nitrogen metabolism</t>
   </si>
   <si>
     <t>Drug metabolism - other enzymes</t>
-  </si>
-  <si>
-    <t>E2983</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E918,E284,E227,E144,E1438,E190,E908,E20,E618,E413,E191,E431,E159,E680,E432,E1222,E22,E288,E632,E912,E40,E209,E290,E1059,E634,E914,E178,E291,E179,E338,E281,E833,E66,E410,E170</t>
-  </si>
-  <si>
-    <t>CE2176,C03758,C05350/C01179,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,,C05589/C00788,C09642,C05580,C00355,C13690,C05580,,C00822/C05604,C00082/CE2174,,C00079/CE2172,C05577/C00544,C05584,C00082/CE2174,,,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$Dopamine$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/3-(4-Hydroxyphenyl)pyruvate$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3,4-Dihydroxymandelate$3,4-Dihydroxy-L-phenylalanine$Dopamine 3-O-sulfate$3,4-Dihydroxymandelate$$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/Homogentisate$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$L-Tyrosine/$$$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>E2139,E1066</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>E1417</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E33</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E833,E227,E2089</t>
-  </si>
-  <si>
-    <t>C02763/C00166,C05350/C01179,</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/3-(4-Hydroxyphenyl)pyruvate$</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E1475,E1587,E1474</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E2839,E33</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E1129,E1119,E2859,E1128,E3153</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2263,E556,E2141,E1950,E1037,E1954,E2142,E2394,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,,C03917/C05293/C00523/C04373/C04295,C11134/tststeroneglc,C04042/C01953/C03681,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C03917/C05293/C00523/C04373/C04295,C18038/C05138/C04518/C05485,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>E2765</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>E506</t>
-  </si>
-  <si>
-    <t>C01045/C01042</t>
-  </si>
-  <si>
-    <t>N-Formyl-L-glutamate/N-Acetyl-L-aspartate</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E1587,E1528,E1634,E1411,E144,E1535,E410,E413</t>
-  </si>
-  <si>
-    <t>,,,,CE5536,,C05589/C00788,C05589/C00788</t>
-  </si>
-  <si>
-    <t>$$$$adrenochrome$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E92</t>
-  </si>
-  <si>
-    <t>C06426/C06427</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E1488,E1403</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>E2383,E3164</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E855</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E1045</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E2570</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E833,E784</t>
-  </si>
-  <si>
-    <t>C02763/C00166,</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E15</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E1451</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E582</t>
-  </si>
-  <si>
-    <t>C00234/C03479</t>
-  </si>
-  <si>
-    <t>10-Formyltetrahydrofolate/5-Formyltetrahydrofolate</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E1671,E582</t>
-  </si>
-  <si>
-    <t>,C00234/C03479</t>
-  </si>
-  <si>
-    <t>$10-Formyltetrahydrofolate/5-Formyltetrahydrofolate</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Geraniol degradation</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>Dynorphin metabolism</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation, peroxisome</t>
-  </si>
-  <si>
-    <t>Polyunsaturated fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>3-Chloroacrylic acid degradation</t>
-  </si>
-  <si>
-    <t>Sphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>O-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>Proteoglycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin K metabolism</t>
-  </si>
-  <si>
-    <t>Glutamate metabolism</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol phosphate metabolism</t>
-  </si>
-  <si>
-    <t>Benzoate degradation via CoA ligation</t>
-  </si>
-  <si>
-    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
-  </si>
-  <si>
-    <t>Pentose and Glucuronate Interconversions</t>
-  </si>
-  <si>
-    <t>Atrazine degradation</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>Carbon fixation</t>
-  </si>
-  <si>
-    <t>Nucleotide Sugar Metabolism</t>
-  </si>
-  <si>
-    <t>1- and 2-Methylnaphthalene degradation</t>
-  </si>
-  <si>
-    <t>Nitrogen metabolism</t>
   </si>
   <si>
     <t>Starch and Sucrose Metabolism</t>
@@ -1060,13 +1060,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.01310902337775836</v>
+        <v>0.002201643669854288</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1083,13 +1083,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>0.0176299557990622</v>
+        <v>0.01855431001159644</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1106,13 +1106,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>0.02507520882001983</v>
+        <v>0.02236937194332869</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1129,13 +1129,13 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0.03682291053931867</v>
+        <v>0.02920959311608208</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1152,13 +1152,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>0.05159577149963866</v>
+        <v>0.04090687551469723</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1175,13 +1175,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>0.0734105309154468</v>
+        <v>0.04512529201189896</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1198,13 +1198,13 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>0.0795280751584007</v>
+        <v>0.04818406413337591</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1221,13 +1221,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>0.08325910488899346</v>
+        <v>0.07635165795532849</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1244,13 +1244,13 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>0.08756155358733467</v>
+        <v>0.08329271776944926</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1267,13 +1267,13 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0.113040116972824</v>
+        <v>0.08450278146585771</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1290,13 +1290,13 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>0.113678761701484</v>
+        <v>0.08598174820591251</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1313,91 +1313,91 @@
         <v>51</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>0.1146031159140183</v>
+        <v>0.09048587418698846</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D14">
-        <v>0.1152753735231341</v>
+        <v>0.09330935614527487</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>0.1408715819902187</v>
+        <v>0.09396480731416279</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>0.09396480731416279</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
         <v>61</v>
       </c>
-      <c r="B16">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>120</v>
-      </c>
-      <c r="D16">
-        <v>0.1461488042217778</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>62</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1411,16 +1411,16 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1655770491252248</v>
+        <v>0.1473420614779584</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1428,508 +1428,520 @@
         <v>67</v>
       </c>
       <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>2</v>
       </c>
-      <c r="C18">
-        <v>6</v>
-      </c>
       <c r="D18">
-        <v>0.1972403825145796</v>
+        <v>0.1667534999411775</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
         <v>2</v>
       </c>
-      <c r="C19">
-        <v>6</v>
-      </c>
       <c r="D19">
-        <v>0.1972403825145796</v>
+        <v>0.1667534999411775</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>0.2501806692324499</v>
+        <v>0.17887094334549</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>27</v>
+      </c>
+      <c r="D21">
+        <v>0.2034587653989009</v>
+      </c>
+      <c r="E21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
         <v>75</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>7</v>
-      </c>
-      <c r="D21">
-        <v>0.2501806692324499</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>0.234264970336633</v>
+      </c>
+      <c r="E22" t="s">
         <v>77</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>0.2664997226937362</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>78</v>
+      </c>
+      <c r="G22" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>0.2664997226937362</v>
+        <v>0.234264970336633</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>81</v>
+      </c>
+      <c r="F23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>0.3129863363640947</v>
+        <v>0.234264970336633</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>0.3360783852372229</v>
+        <v>0.2535755701584848</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>0.3474899581519638</v>
+        <v>0.2938774138249777</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D27">
-        <v>0.3474899581519638</v>
+        <v>0.296247121897111</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="D28">
-        <v>0.3851195778222214</v>
+        <v>0.3161459471269391</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D29">
-        <v>0.3898253810860322</v>
+        <v>0.3232382649031109</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>99</v>
+      </c>
+      <c r="F29" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>0.3898253810860322</v>
+        <v>0.3311036789297659</v>
       </c>
       <c r="E30" t="s">
-        <v>95</v>
+        <v>103</v>
+      </c>
+      <c r="F30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>0.3898253810860322</v>
+        <v>0.3311036789297659</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>105</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B32">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>0.3977916337540546</v>
+        <v>0.3311036789297659</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>0.4262449370598814</v>
+        <v>0.3665484613703971</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D34">
-        <v>0.4416564427488613</v>
+        <v>0.3690526209643535</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>112</v>
+      </c>
+      <c r="F34" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>0.4416564427488613</v>
+        <v>0.3760272936589301</v>
       </c>
       <c r="E35" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D36">
-        <v>0.4416564427488613</v>
+        <v>0.4053545318566075</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>118</v>
+      </c>
+      <c r="F36" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>0.4575385287642225</v>
+        <v>0.4296062251054604</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" t="s">
-        <v>111</v>
-      </c>
-      <c r="G37" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>0.4575385287642225</v>
+        <v>0.4296062251054604</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G38" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>0.4611519134132199</v>
+        <v>0.4296062251054604</v>
       </c>
       <c r="E39" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D40">
-        <v>0.4642779112956085</v>
+        <v>0.4324297070637468</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="G40" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C41">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="D41">
-        <v>0.4807482227189459</v>
+        <v>0.4487319540848053</v>
       </c>
       <c r="E41" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G41" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1938,15 +1950,15 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4831683501117628</v>
+        <v>0.4719248415993009</v>
       </c>
       <c r="E42" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1955,421 +1967,400 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4831683501117628</v>
+        <v>0.4719248415993009</v>
       </c>
       <c r="E43" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>0.4831683501117628</v>
+        <v>0.501924337406094</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>135</v>
+      </c>
+      <c r="F44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>0.4831683501117628</v>
+        <v>0.501924337406094</v>
       </c>
       <c r="E45" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F45" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D46">
-        <v>0.4907480546545436</v>
+        <v>0.5066301406699047</v>
       </c>
       <c r="E46" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B47">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D47">
-        <v>0.4990840490075797</v>
+        <v>0.5230332263323305</v>
       </c>
       <c r="E47" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F47" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G47" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48">
-        <v>0.5140585872506345</v>
+        <v>0.5297558024234886</v>
       </c>
       <c r="E48" t="s">
-        <v>137</v>
-      </c>
-      <c r="F48" t="s">
-        <v>138</v>
-      </c>
-      <c r="G48" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>0.5144619418161039</v>
+        <v>0.5475202097443741</v>
       </c>
       <c r="E49" t="s">
-        <v>141</v>
-      </c>
-      <c r="F49" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D50">
-        <v>0.5144619418161039</v>
+        <v>0.5475202097443741</v>
       </c>
       <c r="E50" t="s">
-        <v>143</v>
-      </c>
-      <c r="F50" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51">
-        <v>0.5355036049814289</v>
+        <v>0.5475202097443741</v>
       </c>
       <c r="E51" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D52">
-        <v>0.5355036049814289</v>
+        <v>0.5475202097443741</v>
       </c>
       <c r="E52" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53">
-        <v>0.5523268516495521</v>
+        <v>0.5641753920102183</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54">
-        <v>0.5523268516495521</v>
+        <v>0.5784944790843851</v>
       </c>
       <c r="E54" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D55">
-        <v>0.5523268516495521</v>
+        <v>0.5784944790843851</v>
       </c>
       <c r="E55" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D56">
-        <v>0.5523268516495521</v>
+        <v>0.5869313120787886</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D57">
-        <v>0.5695702593233727</v>
+        <v>0.5917547604241945</v>
       </c>
       <c r="E57" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D58">
-        <v>0.5739231273423976</v>
+        <v>0.5917547604241945</v>
       </c>
       <c r="E58" t="s">
-        <v>155</v>
-      </c>
-      <c r="F58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G58" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D59">
-        <v>0.580763348515151</v>
+        <v>0.6041747197526092</v>
       </c>
       <c r="E59" t="s">
-        <v>159</v>
+        <v>163</v>
+      </c>
+      <c r="F59" t="s">
+        <v>164</v>
+      </c>
+      <c r="G59" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D60">
-        <v>0.5925278566746778</v>
+        <v>0.6066116535856541</v>
       </c>
       <c r="E60" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="F60" t="s">
+        <v>164</v>
+      </c>
+      <c r="G60" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D61">
-        <v>0.5925278566746778</v>
+        <v>0.6129308751113427</v>
       </c>
       <c r="E61" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F61" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="G61" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D62">
-        <v>0.5973008856994</v>
-      </c>
-      <c r="E62" t="s">
-        <v>93</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D63">
-        <v>0.603569687904405</v>
-      </c>
-      <c r="E63" t="s">
-        <v>78</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>0.6099225223105494</v>
-      </c>
-      <c r="E64" t="s">
-        <v>169</v>
-      </c>
-      <c r="F64" t="s">
-        <v>170</v>
-      </c>
-      <c r="G64" t="s">
-        <v>171</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2380,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="C65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2394,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2408,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D67">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2422,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2436,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D69">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2450,10 +2441,10 @@
         <v>0</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2464,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2478,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D72">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2492,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2509,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2520,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2537,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2548,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2562,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D78">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2576,10 +2567,10 @@
         <v>0</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2590,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="C80">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D80">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2604,10 +2595,10 @@
         <v>0</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2618,10 +2609,10 @@
         <v>0</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2632,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2646,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2660,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2677,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2688,10 +2679,10 @@
         <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2702,10 +2693,10 @@
         <v>0</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2716,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2730,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2747,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2761,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2775,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2789,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2800,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D95">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2814,10 +2805,10 @@
         <v>0</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2828,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D97">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2845,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2859,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2873,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2884,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2898,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2915,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2926,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D104">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2940,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2957,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2971,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2982,10 +2973,10 @@
         <v>0</v>
       </c>
       <c r="C108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2999,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3010,10 +3001,10 @@
         <v>0</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3027,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3038,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D112">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3055,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3066,10 +3057,10 @@
         <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D114">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3083,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3097,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3111,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3125,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3139,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3153,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.6111493924471858</v>
+        <v>0.6139728744054722</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -40,13 +40,13 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E1164,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1950,E1954,E1951,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C05487/C05475/C05478,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1164,E1950,E1954,E1951,E1955,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
@@ -76,13 +76,13 @@
     <t>Arachidonic acid metabolism</t>
   </si>
   <si>
-    <t>E2298,E1015,E92,E975,E2296,E2297,E1017,E2513,E2295</t>
-  </si>
-  <si>
-    <t>C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C06426/C06427,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C00909,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00909</t>
-  </si>
-  <si>
-    <t>Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$Leukotriene A4$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Leukotriene A4</t>
+    <t>E2298,E975,E92,E1015,E2296,E2297,E1017,E2513,E2295</t>
+  </si>
+  <si>
+    <t>C00909,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C06426/C06427,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C00909,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00909</t>
+  </si>
+  <si>
+    <t>Leukotriene A4$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$Leukotriene A4$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Leukotriene A4</t>
   </si>
   <si>
     <t>Androgen and estrogen biosynthesis and metabolism</t>
@@ -112,13 +112,13 @@
     <t>Omega-3 fatty acid metabolism</t>
   </si>
   <si>
-    <t>E2325,E92,E2326</t>
-  </si>
-  <si>
-    <t>C16300,C06426/C06427,C16300</t>
-  </si>
-  <si>
-    <t>Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid</t>
+    <t>E92,E2325,E2326</t>
+  </si>
+  <si>
+    <t>C06426/C06427,,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$</t>
   </si>
   <si>
     <t>CoA Catabolism</t>
@@ -184,13 +184,13 @@
     <t>Leukotriene metabolism</t>
   </si>
   <si>
-    <t>E2298,E1015,E975,E1286,E2296,E1302,E2297,E1017,E1899,E2779,E1820,E2295</t>
-  </si>
-  <si>
-    <t>C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,,C00909,,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,,,C00909</t>
-  </si>
-  <si>
-    <t>Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$$Leukotriene A4$$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$$$Leukotriene A4</t>
+    <t>E2298,E975,E1015,E1286,E2296,E1302,E2297,E1017,E1899,E2779,E1820,E2295</t>
+  </si>
+  <si>
+    <t>C00909,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,C00909,,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,,,C00909</t>
+  </si>
+  <si>
+    <t>Leukotriene A4$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$Leukotriene A4$$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$$$Leukotriene A4</t>
   </si>
   <si>
     <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
@@ -301,13 +301,13 @@
     <t>Tyrosine metabolism</t>
   </si>
   <si>
-    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E287,E1222,E22,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E283,E833,E66,E410,E170</t>
-  </si>
-  <si>
-    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,C03758,,C00822/C05604,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C03758,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$Dopamine$$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$Dopamine$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
+    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E283,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E833,E66,E410,E170</t>
+  </si>
+  <si>
+    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C03758,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Dopamine$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
   </si>
   <si>
     <t>Carnitine shuttle</t>
@@ -1066,7 +1066,7 @@
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.002201643669854288</v>
+        <v>0.001882321305524277</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0.01855431001159644</v>
+        <v>0.01986521234937228</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1112,7 +1112,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.02236937194332869</v>
+        <v>0.02403320952589032</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1135,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>0.02920959311608208</v>
+        <v>0.03141123678593637</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1158,7 +1158,7 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>0.04090687551469723</v>
+        <v>0.04327658358683047</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.04512529201189896</v>
+        <v>0.0474950000840322</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>0.04818406413337591</v>
+        <v>0.0503689013630023</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>0.07635165795532849</v>
+        <v>0.07788104401606696</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>0.08329271776944926</v>
+        <v>0.08344397573150031</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.08450278146585771</v>
+        <v>0.0845532007865414</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0.08598174820591251</v>
+        <v>0.08613300616796356</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1319,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.09048587418698846</v>
+        <v>0.08986403589855632</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1365,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>0.09396480731416279</v>
+        <v>0.09374632359120015</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1388,7 +1388,7 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.09396480731416279</v>
+        <v>0.09374632359120015</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1411,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1473420614779584</v>
+        <v>0.1467874489504378</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.1667534999411775</v>
+        <v>0.1644678240701837</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1667534999411775</v>
+        <v>0.1644678240701837</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.17887094334549</v>
+        <v>0.1772071057629284</v>
       </c>
       <c r="E20" t="s">
         <v>71</v>
@@ -1497,7 +1497,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0.2034587653989009</v>
+        <v>0.2012067024083629</v>
       </c>
       <c r="E21" t="s">
         <v>73</v>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>0.234264970336633</v>
+        <v>0.2332733903631872</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.234264970336633</v>
+        <v>0.2332733903631872</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
@@ -1566,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.234264970336633</v>
+        <v>0.2332733903631872</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -1589,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2535755701584848</v>
+        <v>0.2538780860825868</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
@@ -1606,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.2938774138249777</v>
+        <v>0.2915245121930724</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -1629,7 +1629,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>0.296247121897111</v>
+        <v>0.2937261558629267</v>
       </c>
       <c r="E27" t="s">
         <v>93</v>
@@ -1652,7 +1652,7 @@
         <v>152</v>
       </c>
       <c r="D28">
-        <v>0.3161459471269391</v>
+        <v>0.3148182383489353</v>
       </c>
       <c r="E28" t="s">
         <v>95</v>
@@ -1675,7 +1675,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.3232382649031109</v>
+        <v>0.3216248466412329</v>
       </c>
       <c r="E29" t="s">
         <v>99</v>
@@ -1698,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>0.3311036789297659</v>
+        <v>0.3293558091460648</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>0.3311036789297659</v>
+        <v>0.3293558091460648</v>
       </c>
       <c r="E31" t="s">
         <v>105</v>
@@ -1744,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>0.3311036789297659</v>
+        <v>0.3293558091460648</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>0.3665484613703971</v>
+        <v>0.3640947210971244</v>
       </c>
       <c r="E33" t="s">
         <v>108</v>
@@ -1790,7 +1790,7 @@
         <v>43</v>
       </c>
       <c r="D34">
-        <v>0.3690526209643535</v>
+        <v>0.367220718979513</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -1813,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>0.3760272936589301</v>
+        <v>0.3735399405052016</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
@@ -1830,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>0.4053545318566075</v>
+        <v>0.4027159207408279</v>
       </c>
       <c r="E36" t="s">
         <v>118</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>0.4296062251054604</v>
+        <v>0.4265810658644393</v>
       </c>
       <c r="E37" t="s">
         <v>120</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>0.4296062251054604</v>
+        <v>0.4265810658644393</v>
       </c>
       <c r="E38" t="s">
         <v>122</v>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>0.4296062251054604</v>
+        <v>0.4265810658644393</v>
       </c>
       <c r="E39" t="s">
         <v>124</v>
@@ -1904,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="D40">
-        <v>0.4324297070637468</v>
+        <v>0.4292532898606746</v>
       </c>
       <c r="E40" t="s">
         <v>126</v>
@@ -1927,7 +1927,7 @@
         <v>120</v>
       </c>
       <c r="D41">
-        <v>0.4487319540848053</v>
+        <v>0.4462277944908489</v>
       </c>
       <c r="E41" t="s">
         <v>128</v>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4719248415993009</v>
+        <v>0.4682442311893918</v>
       </c>
       <c r="E42" t="s">
         <v>122</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4719248415993009</v>
+        <v>0.4682442311893918</v>
       </c>
       <c r="E43" t="s">
         <v>133</v>
@@ -1984,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>0.501924337406094</v>
+        <v>0.4963277928102049</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
@@ -2007,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="D45">
-        <v>0.501924337406094</v>
+        <v>0.4963277928102049</v>
       </c>
       <c r="E45" t="s">
         <v>137</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <v>0.5066301406699047</v>
+        <v>0.5013193055578898</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -2053,7 +2053,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>0.5230332263323305</v>
+        <v>0.5184954874707988</v>
       </c>
       <c r="E47" t="s">
         <v>143</v>
@@ -2076,7 +2076,7 @@
         <v>9</v>
       </c>
       <c r="D48">
-        <v>0.5297558024234886</v>
+        <v>0.5259407404917564</v>
       </c>
       <c r="E48" t="s">
         <v>122</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>0.5475202097443741</v>
+        <v>0.5441757281390228</v>
       </c>
       <c r="E49" t="s">
         <v>120</v>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>0.5475202097443741</v>
+        <v>0.5441757281390228</v>
       </c>
       <c r="E50" t="s">
         <v>149</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>0.5475202097443741</v>
+        <v>0.5441757281390228</v>
       </c>
       <c r="E51" t="s">
         <v>151</v>
@@ -2144,7 +2144,7 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>0.5475202097443741</v>
+        <v>0.5441757281390228</v>
       </c>
       <c r="E52" t="s">
         <v>153</v>
@@ -2161,7 +2161,7 @@
         <v>11</v>
       </c>
       <c r="D53">
-        <v>0.5641753920102183</v>
+        <v>0.5615031680139829</v>
       </c>
       <c r="E53" t="s">
         <v>122</v>
@@ -2178,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="D54">
-        <v>0.5784944790843851</v>
+        <v>0.5760239323708846</v>
       </c>
       <c r="E54" t="s">
         <v>122</v>
@@ -2195,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="D55">
-        <v>0.5784944790843851</v>
+        <v>0.5760239323708846</v>
       </c>
       <c r="E55" t="s">
         <v>157</v>
@@ -2212,7 +2212,7 @@
         <v>13</v>
       </c>
       <c r="D56">
-        <v>0.5869313120787886</v>
+        <v>0.5844439589250601</v>
       </c>
       <c r="E56" t="s">
         <v>122</v>
@@ -2229,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>0.5917547604241945</v>
+        <v>0.5897716004773029</v>
       </c>
       <c r="E57" t="s">
         <v>160</v>
@@ -2246,7 +2246,7 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.5917547604241945</v>
+        <v>0.5897716004773029</v>
       </c>
       <c r="E58" t="s">
         <v>153</v>
@@ -2263,7 +2263,7 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>0.6041747197526092</v>
+        <v>0.601973076082755</v>
       </c>
       <c r="E59" t="s">
         <v>163</v>
@@ -2286,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="D60">
-        <v>0.6066116535856541</v>
+        <v>0.6041243004319256</v>
       </c>
       <c r="E60" t="s">
         <v>163</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="D61">
-        <v>0.6129308751113427</v>
+        <v>0.6100905867128283</v>
       </c>
       <c r="E61" t="s">
         <v>168</v>
@@ -2332,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="D62">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="D69">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="D78">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="D80">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="D104">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="D112">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="D114">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.6139728744054722</v>
+        <v>0.611267037528781</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -112,13 +112,13 @@
     <t>Omega-3 fatty acid metabolism</t>
   </si>
   <si>
-    <t>E92,E2325,E2326</t>
-  </si>
-  <si>
-    <t>C06426/C06427,,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$</t>
+    <t>E2325,E92,E2326</t>
+  </si>
+  <si>
+    <t>C16300,C06426/C06427,C16300</t>
+  </si>
+  <si>
+    <t>Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid</t>
   </si>
   <si>
     <t>CoA Catabolism</t>
@@ -1066,7 +1066,7 @@
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.001882321305524277</v>
+        <v>0.002453740273272718</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0.01986521234937228</v>
+        <v>0.01902489033797751</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1112,7 +1112,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.02403320952589032</v>
+        <v>0.02312566175358397</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1135,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>0.03141123678593637</v>
+        <v>0.0302179795297558</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1158,7 +1158,7 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>0.04327658358683047</v>
+        <v>0.04267155173862624</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.0474950000840322</v>
+        <v>0.04660425875195375</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>0.0503689013630023</v>
+        <v>0.04949496647115174</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>0.07788104401606696</v>
+        <v>0.07862052738609435</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>0.08344397573150031</v>
+        <v>0.08401539469924875</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.0845532007865414</v>
+        <v>0.08505739399337826</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0.08613300616796356</v>
+        <v>0.086704425135712</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1319,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.08986403589855632</v>
+        <v>0.09046906774676056</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1342,7 +1342,7 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>0.09330935614527487</v>
+        <v>0.09314129174299592</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1365,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>0.09374632359120015</v>
+        <v>0.09377993647165594</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1388,7 +1388,7 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.09374632359120015</v>
+        <v>0.09377993647165594</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1411,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1467874489504378</v>
+        <v>0.147560545200921</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.1644678240701837</v>
+        <v>0.1659804036906943</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1644678240701837</v>
+        <v>0.1659804036906943</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.1772071057629284</v>
+        <v>0.1773751701652073</v>
       </c>
       <c r="E20" t="s">
         <v>71</v>
@@ -1497,7 +1497,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0.2012067024083629</v>
+        <v>0.2011562830876792</v>
       </c>
       <c r="E21" t="s">
         <v>73</v>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>0.2332733903631872</v>
+        <v>0.2336095191677451</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.2332733903631872</v>
+        <v>0.2336095191677451</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
@@ -1566,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.2332733903631872</v>
+        <v>0.2336095191677451</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -1589,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2538780860825868</v>
+        <v>0.2537604410009916</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
@@ -1606,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.2915245121930724</v>
+        <v>0.2928186080906203</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -1629,7 +1629,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>0.2937261558629267</v>
+        <v>0.2948353809179677</v>
       </c>
       <c r="E27" t="s">
         <v>93</v>
@@ -1652,7 +1652,7 @@
         <v>152</v>
       </c>
       <c r="D28">
-        <v>0.3148182383489353</v>
+        <v>0.3186501067208954</v>
       </c>
       <c r="E28" t="s">
         <v>95</v>
@@ -1675,7 +1675,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.3216248466412329</v>
+        <v>0.3264146821061831</v>
       </c>
       <c r="E29" t="s">
         <v>99</v>
@@ -1698,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>0.3293558091460648</v>
+        <v>0.3337422900455455</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>0.3293558091460648</v>
+        <v>0.3337422900455455</v>
       </c>
       <c r="E31" t="s">
         <v>105</v>
@@ -1744,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>0.3293558091460648</v>
+        <v>0.3337422900455455</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>0.3640947210971244</v>
+        <v>0.3678761701484008</v>
       </c>
       <c r="E33" t="s">
         <v>108</v>
@@ -1790,7 +1790,7 @@
         <v>43</v>
       </c>
       <c r="D34">
-        <v>0.367220718979513</v>
+        <v>0.3704139426228131</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -1813,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>0.3735399405052016</v>
+        <v>0.3774558410783012</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
@@ -1830,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>0.4027159207408279</v>
+        <v>0.4045646291658964</v>
       </c>
       <c r="E36" t="s">
         <v>118</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>0.4265810658644393</v>
+        <v>0.4278751617619872</v>
       </c>
       <c r="E37" t="s">
         <v>120</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>0.4265810658644393</v>
+        <v>0.4278751617619872</v>
       </c>
       <c r="E38" t="s">
         <v>122</v>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>0.4265810658644393</v>
+        <v>0.4278751617619872</v>
       </c>
       <c r="E39" t="s">
         <v>124</v>
@@ -1904,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="D40">
-        <v>0.4292532898606746</v>
+        <v>0.4309003210030083</v>
       </c>
       <c r="E40" t="s">
         <v>126</v>
@@ -1927,7 +1927,7 @@
         <v>120</v>
       </c>
       <c r="D41">
-        <v>0.4462277944908489</v>
+        <v>0.4489336313675401</v>
       </c>
       <c r="E41" t="s">
         <v>128</v>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4682442311893918</v>
+        <v>0.4707483907833482</v>
       </c>
       <c r="E42" t="s">
         <v>122</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4682442311893918</v>
+        <v>0.4707483907833482</v>
       </c>
       <c r="E43" t="s">
         <v>133</v>
@@ -1984,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>0.4963277928102049</v>
+        <v>0.5008991445521924</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
@@ -2007,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="D45">
-        <v>0.4963277928102049</v>
+        <v>0.5008991445521924</v>
       </c>
       <c r="E45" t="s">
         <v>137</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <v>0.5013193055578898</v>
+        <v>0.5052688190114452</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -2053,7 +2053,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>0.5184954874707988</v>
+        <v>0.5223273558427589</v>
       </c>
       <c r="E47" t="s">
         <v>143</v>
@@ -2076,7 +2076,7 @@
         <v>9</v>
       </c>
       <c r="D48">
-        <v>0.5259407404917564</v>
+        <v>0.5299238668257676</v>
       </c>
       <c r="E48" t="s">
         <v>122</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>0.5441757281390228</v>
+        <v>0.5457891464009008</v>
       </c>
       <c r="E49" t="s">
         <v>120</v>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>0.5441757281390228</v>
+        <v>0.5457891464009008</v>
       </c>
       <c r="E50" t="s">
         <v>149</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>0.5441757281390228</v>
+        <v>0.5457891464009008</v>
       </c>
       <c r="E51" t="s">
         <v>151</v>
@@ -2144,7 +2144,7 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>0.5441757281390228</v>
+        <v>0.5457891464009008</v>
       </c>
       <c r="E52" t="s">
         <v>153</v>
@@ -2161,7 +2161,7 @@
         <v>11</v>
       </c>
       <c r="D53">
-        <v>0.5615031680139829</v>
+        <v>0.5620241676610477</v>
       </c>
       <c r="E53" t="s">
         <v>122</v>
@@ -2178,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="D54">
-        <v>0.5760239323708846</v>
+        <v>0.5763768676156703</v>
       </c>
       <c r="E54" t="s">
         <v>122</v>
@@ -2195,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="D55">
-        <v>0.5760239323708846</v>
+        <v>0.5763768676156703</v>
       </c>
       <c r="E55" t="s">
         <v>157</v>
@@ -2212,7 +2212,7 @@
         <v>13</v>
       </c>
       <c r="D56">
-        <v>0.5844439589250601</v>
+        <v>0.5852338616157712</v>
       </c>
       <c r="E56" t="s">
         <v>122</v>
@@ -2229,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>0.5897716004773029</v>
+        <v>0.5909312448530277</v>
       </c>
       <c r="E57" t="s">
         <v>160</v>
@@ -2246,7 +2246,7 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.5897716004773029</v>
+        <v>0.5909312448530277</v>
       </c>
       <c r="E58" t="s">
         <v>153</v>
@@ -2263,7 +2263,7 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>0.601973076082755</v>
+        <v>0.604527654997395</v>
       </c>
       <c r="E59" t="s">
         <v>163</v>
@@ -2286,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="D60">
-        <v>0.6041243004319256</v>
+        <v>0.6064940085040588</v>
       </c>
       <c r="E60" t="s">
         <v>163</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="D61">
-        <v>0.6100905867128283</v>
+        <v>0.6124266819045058</v>
       </c>
       <c r="E61" t="s">
         <v>168</v>
@@ -2332,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="D62">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="D69">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="D78">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="D80">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="D104">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="D112">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="D114">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.611267037528781</v>
+        <v>0.6137375842422816</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -40,13 +40,13 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1164,E1950,E1954,E1951,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+    <t>E2263,E2398,E1164,E2266,E2153,E2356,E2457,E1118,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1950,E1954,E1951,E1955,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,C05487/C05475/C05478,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
@@ -301,13 +301,13 @@
     <t>Tyrosine metabolism</t>
   </si>
   <si>
-    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E283,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E833,E66,E410,E170</t>
-  </si>
-  <si>
-    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C03758,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Dopamine$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
+    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E288,E335,E632,E912,E40,E12,E283,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E833,E66,E410,E170</t>
+  </si>
+  <si>
+    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C03758,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$Dopamine$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
   </si>
   <si>
     <t>Carnitine shuttle</t>
@@ -1066,7 +1066,7 @@
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.002453740273272718</v>
+        <v>0.002386514512361137</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0.01902489033797751</v>
+        <v>0.01830221340817801</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1112,7 +1112,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.02312566175358397</v>
+        <v>0.02193240449740341</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1135,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>0.0302179795297558</v>
+        <v>0.02838607754491521</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1158,7 +1158,7 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>0.04267155173862624</v>
+        <v>0.04023461790558142</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.04660425875195375</v>
+        <v>0.04406648627754155</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>0.04949496647115174</v>
+        <v>0.04719248415993008</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>0.07862052738609435</v>
+        <v>0.07467101393253894</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>0.08401539469924875</v>
+        <v>0.0809398161375439</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.08505739399337826</v>
+        <v>0.08191458967076183</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0.086704425135712</v>
+        <v>0.08354481437286768</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1319,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.09046906774676056</v>
+        <v>0.08764558578847415</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1342,7 +1342,7 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>0.09314129174299592</v>
+        <v>0.09090603519268584</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1365,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>0.09377993647165594</v>
+        <v>0.09156148636157375</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1388,7 +1388,7 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.09377993647165594</v>
+        <v>0.09156148636157375</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1411,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.147560545200921</v>
+        <v>0.1435942253071377</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.1659804036906943</v>
+        <v>0.1609720845027815</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1659804036906943</v>
+        <v>0.1609720845027815</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.1773751701652073</v>
+        <v>0.1729718828254987</v>
       </c>
       <c r="E20" t="s">
         <v>71</v>
@@ -1497,7 +1497,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0.2011562830876792</v>
+        <v>0.1975092855582259</v>
       </c>
       <c r="E21" t="s">
         <v>73</v>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>0.2336095191677451</v>
+        <v>0.2284499420177812</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.2336095191677451</v>
+        <v>0.2284499420177812</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
@@ -1566,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.2336095191677451</v>
+        <v>0.2284499420177812</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -1589,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2537604410009916</v>
+        <v>0.2490042184164972</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
@@ -1606,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.2928186080906203</v>
+        <v>0.2886169980336465</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -1629,7 +1629,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>0.2948353809179677</v>
+        <v>0.2919446731987698</v>
       </c>
       <c r="E27" t="s">
         <v>93</v>
@@ -1652,7 +1652,7 @@
         <v>152</v>
       </c>
       <c r="D28">
-        <v>0.3186501067208954</v>
+        <v>0.315036722071898</v>
       </c>
       <c r="E28" t="s">
         <v>95</v>
@@ -1675,7 +1675,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.3264146821061831</v>
+        <v>0.3212214920757634</v>
       </c>
       <c r="E29" t="s">
         <v>99</v>
@@ -1698,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>0.3337422900455455</v>
+        <v>0.328834809499</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>0.3337422900455455</v>
+        <v>0.328834809499</v>
       </c>
       <c r="E31" t="s">
         <v>105</v>
@@ -1744,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>0.3337422900455455</v>
+        <v>0.328834809499</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>0.3678761701484008</v>
+        <v>0.363674560091427</v>
       </c>
       <c r="E33" t="s">
         <v>108</v>
@@ -1790,7 +1790,7 @@
         <v>43</v>
       </c>
       <c r="D34">
-        <v>0.3704139426228131</v>
+        <v>0.3666661064519924</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -1813,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>0.3774558410783012</v>
+        <v>0.3734054889833784</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
@@ -1830,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>0.4045646291658964</v>
+        <v>0.4026486949799163</v>
       </c>
       <c r="E36" t="s">
         <v>118</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>0.4278751617619872</v>
+        <v>0.4266482916253508</v>
       </c>
       <c r="E37" t="s">
         <v>120</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>0.4278751617619872</v>
+        <v>0.4266482916253508</v>
       </c>
       <c r="E38" t="s">
         <v>122</v>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>0.4278751617619872</v>
+        <v>0.4266482916253508</v>
       </c>
       <c r="E39" t="s">
         <v>124</v>
@@ -1904,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="D40">
-        <v>0.4309003210030083</v>
+        <v>0.4299087410295625</v>
       </c>
       <c r="E40" t="s">
         <v>126</v>
@@ -1927,7 +1927,7 @@
         <v>120</v>
       </c>
       <c r="D41">
-        <v>0.4489336313675401</v>
+        <v>0.44733701954589</v>
       </c>
       <c r="E41" t="s">
         <v>128</v>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4707483907833482</v>
+        <v>0.4689164887985076</v>
       </c>
       <c r="E42" t="s">
         <v>122</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4707483907833482</v>
+        <v>0.4689164887985076</v>
       </c>
       <c r="E43" t="s">
         <v>133</v>
@@ -1984,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>0.5008991445521924</v>
+        <v>0.4975714693870691</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
@@ -2007,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="D45">
-        <v>0.5008991445521924</v>
+        <v>0.4975714693870691</v>
       </c>
       <c r="E45" t="s">
         <v>137</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <v>0.5052688190114452</v>
+        <v>0.5018234987647266</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -2053,7 +2053,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>0.5223273558427589</v>
+        <v>0.5190164871178635</v>
       </c>
       <c r="E47" t="s">
         <v>143</v>
@@ -2076,7 +2076,7 @@
         <v>9</v>
       </c>
       <c r="D48">
-        <v>0.5299238668257676</v>
+        <v>0.5263104821767701</v>
       </c>
       <c r="E48" t="s">
         <v>122</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>0.5457891464009008</v>
+        <v>0.5439404379758324</v>
       </c>
       <c r="E49" t="s">
         <v>120</v>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>0.5457891464009008</v>
+        <v>0.5439404379758324</v>
       </c>
       <c r="E50" t="s">
         <v>149</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>0.5457891464009008</v>
+        <v>0.5439404379758324</v>
       </c>
       <c r="E51" t="s">
         <v>151</v>
@@ -2144,7 +2144,7 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>0.5457891464009008</v>
+        <v>0.5439404379758324</v>
       </c>
       <c r="E52" t="s">
         <v>153</v>
@@ -2161,7 +2161,7 @@
         <v>11</v>
       </c>
       <c r="D53">
-        <v>0.5620241676610477</v>
+        <v>0.5603939429589418</v>
       </c>
       <c r="E53" t="s">
         <v>122</v>
@@ -2178,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="D54">
-        <v>0.5763768676156703</v>
+        <v>0.5748474815549318</v>
       </c>
       <c r="E54" t="s">
         <v>122</v>
@@ -2195,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="D55">
-        <v>0.5763768676156703</v>
+        <v>0.5748474815549318</v>
       </c>
       <c r="E55" t="s">
         <v>157</v>
@@ -2212,7 +2212,7 @@
         <v>13</v>
       </c>
       <c r="D56">
-        <v>0.5852338616157712</v>
+        <v>0.5835868304734374</v>
       </c>
       <c r="E56" t="s">
         <v>122</v>
@@ -2229,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>0.5909312448530277</v>
+        <v>0.5897043747163914</v>
       </c>
       <c r="E57" t="s">
         <v>160</v>
@@ -2246,7 +2246,7 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.5909312448530277</v>
+        <v>0.5897043747163914</v>
       </c>
       <c r="E58" t="s">
         <v>153</v>
@@ -2263,7 +2263,7 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>0.604527654997395</v>
+        <v>0.6019898825229828</v>
       </c>
       <c r="E59" t="s">
         <v>163</v>
@@ -2286,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="D60">
-        <v>0.6064940085040588</v>
+        <v>0.6043259777146602</v>
       </c>
       <c r="E60" t="s">
         <v>163</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="D61">
-        <v>0.6124266819045058</v>
+        <v>0.6105611670392094</v>
       </c>
       <c r="E61" t="s">
         <v>168</v>
@@ -2332,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="D62">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="D69">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="D78">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="D80">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="D104">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="D112">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="D114">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.6137375842422816</v>
+        <v>0.6119561015781247</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -40,13 +40,13 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E2398,E1164,E2266,E2153,E2356,E2457,E1118,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1950,E1954,E1951,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,C05487/C05475/C05478,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1164,E1950,E1954,E1951,E1955,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
@@ -76,13 +76,13 @@
     <t>Arachidonic acid metabolism</t>
   </si>
   <si>
-    <t>E2298,E975,E92,E1015,E2296,E2297,E1017,E2513,E2295</t>
-  </si>
-  <si>
-    <t>C00909,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C06426/C06427,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C00909,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00909</t>
-  </si>
-  <si>
-    <t>Leukotriene A4$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$Leukotriene A4$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Leukotriene A4</t>
+    <t>E2298,E1015,E92,E975,E2296,E2297,E1017,E2513,E2295</t>
+  </si>
+  <si>
+    <t>C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C06426/C06427,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C00909,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00909</t>
+  </si>
+  <si>
+    <t>Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$Leukotriene A4$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Leukotriene A4</t>
   </si>
   <si>
     <t>Androgen and estrogen biosynthesis and metabolism</t>
@@ -184,13 +184,13 @@
     <t>Leukotriene metabolism</t>
   </si>
   <si>
-    <t>E2298,E975,E1015,E1286,E2296,E1302,E2297,E1017,E1899,E2779,E1820,E2295</t>
-  </si>
-  <si>
-    <t>C00909,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,C00909,,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,,,C00909</t>
-  </si>
-  <si>
-    <t>Leukotriene A4$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$Leukotriene A4$$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$$$Leukotriene A4</t>
+    <t>E2298,E1015,E975,E1286,E2296,E1302,E2297,E1017,E1899,E2779,E1820,E2295</t>
+  </si>
+  <si>
+    <t>C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,,C00909,,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,,,,C00909</t>
+  </si>
+  <si>
+    <t>Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$$Leukotriene A4$$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$$$$Leukotriene A4</t>
   </si>
   <si>
     <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
@@ -301,13 +301,13 @@
     <t>Tyrosine metabolism</t>
   </si>
   <si>
-    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E288,E335,E632,E912,E40,E12,E283,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E833,E66,E410,E170</t>
-  </si>
-  <si>
-    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C03758,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$Dopamine$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
+    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E283,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E833,E66,E410,E170</t>
+  </si>
+  <si>
+    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C03758,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Dopamine$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
   </si>
   <si>
     <t>Carnitine shuttle</t>
@@ -1066,7 +1066,7 @@
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.002386514512361137</v>
+        <v>0.002151224349170602</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0.01830221340817801</v>
+        <v>0.01909211609888909</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1112,7 +1112,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.02193240449740341</v>
+        <v>0.02317608107426766</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1135,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>0.02838607754491521</v>
+        <v>0.02974739920337473</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1158,7 +1158,7 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>0.04023461790558142</v>
+        <v>0.04136064940085041</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.04406648627754155</v>
+        <v>0.04537738861531739</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>0.04719248415993008</v>
+        <v>0.0482344834540596</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>0.07467101393253894</v>
+        <v>0.07604914203122637</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>0.0809398161375439</v>
+        <v>0.08233475067645922</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.08191458967076183</v>
+        <v>0.08325910488899346</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0.08354481437286768</v>
+        <v>0.08517503907497354</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1319,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.08764558578847415</v>
+        <v>0.08914135896875683</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1342,7 +1342,7 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>0.09090603519268584</v>
+        <v>0.09154467992134586</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1365,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>0.09156148636157375</v>
+        <v>0.09189761516613167</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1388,7 +1388,7 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.09156148636157375</v>
+        <v>0.09189761516613167</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1411,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1435942253071377</v>
+        <v>0.1442496764760256</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.1609720845027815</v>
+        <v>0.1630560830910405</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1609720845027815</v>
+        <v>0.1630560830910405</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.1729718828254987</v>
+        <v>0.1747365590494278</v>
       </c>
       <c r="E20" t="s">
         <v>71</v>
@@ -1497,7 +1497,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0.1975092855582259</v>
+        <v>0.1987361556948623</v>
       </c>
       <c r="E21" t="s">
         <v>73</v>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>0.2284499420177812</v>
+        <v>0.2302650375623939</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.2284499420177812</v>
+        <v>0.2302650375623939</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
@@ -1566,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.2284499420177812</v>
+        <v>0.2302650375623939</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -1589,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2490042184164972</v>
+        <v>0.2507857010806541</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
@@ -1606,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.2886169980336465</v>
+        <v>0.2903312549368918</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -1629,7 +1629,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>0.2919446731987698</v>
+        <v>0.2925328986067461</v>
       </c>
       <c r="E27" t="s">
         <v>93</v>
@@ -1652,7 +1652,7 @@
         <v>152</v>
       </c>
       <c r="D28">
-        <v>0.315036722071898</v>
+        <v>0.3142804322616427</v>
       </c>
       <c r="E28" t="s">
         <v>95</v>
@@ -1675,7 +1675,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.3212214920757634</v>
+        <v>0.3208853632712055</v>
       </c>
       <c r="E29" t="s">
         <v>99</v>
@@ -1698,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>0.328834809499</v>
+        <v>0.3288684223794558</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>0.328834809499</v>
+        <v>0.3288684223794558</v>
       </c>
       <c r="E31" t="s">
         <v>105</v>
@@ -1744,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>0.328834809499</v>
+        <v>0.3288684223794558</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>0.363674560091427</v>
+        <v>0.3622123997916001</v>
       </c>
       <c r="E33" t="s">
         <v>108</v>
@@ -1790,7 +1790,7 @@
         <v>43</v>
       </c>
       <c r="D34">
-        <v>0.3666661064519924</v>
+        <v>0.3653888169946723</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -1813,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>0.3734054889833784</v>
+        <v>0.3728676828960858</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
@@ -1830,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>0.4026486949799163</v>
+        <v>0.4008672123157594</v>
       </c>
       <c r="E36" t="s">
         <v>118</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>0.4266482916253508</v>
+        <v>0.4251357120048402</v>
       </c>
       <c r="E37" t="s">
         <v>120</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>0.4266482916253508</v>
+        <v>0.4251357120048402</v>
       </c>
       <c r="E38" t="s">
         <v>122</v>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>0.4266482916253508</v>
+        <v>0.4251357120048402</v>
       </c>
       <c r="E39" t="s">
         <v>124</v>
@@ -1904,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="D40">
-        <v>0.4299087410295625</v>
+        <v>0.4276566780390246</v>
       </c>
       <c r="E40" t="s">
         <v>126</v>
@@ -1927,7 +1927,7 @@
         <v>120</v>
       </c>
       <c r="D41">
-        <v>0.44733701954589</v>
+        <v>0.4449168921530731</v>
       </c>
       <c r="E41" t="s">
         <v>128</v>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4689164887985076</v>
+        <v>0.4674375220584528</v>
       </c>
       <c r="E42" t="s">
         <v>122</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4689164887985076</v>
+        <v>0.4674375220584528</v>
       </c>
       <c r="E43" t="s">
         <v>133</v>
@@ -1984,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>0.4975714693870691</v>
+        <v>0.4969664375388649</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
@@ -2007,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="D45">
-        <v>0.4975714693870691</v>
+        <v>0.4969664375388649</v>
       </c>
       <c r="E45" t="s">
         <v>137</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <v>0.5018234987647266</v>
+        <v>0.5015209828406245</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -2053,7 +2053,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>0.5190164871178635</v>
+        <v>0.517991294263962</v>
       </c>
       <c r="E47" t="s">
         <v>143</v>
@@ -2076,7 +2076,7 @@
         <v>9</v>
       </c>
       <c r="D48">
-        <v>0.5263104821767701</v>
+        <v>0.5254197408446917</v>
       </c>
       <c r="E48" t="s">
         <v>122</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>0.5439404379758324</v>
+        <v>0.5425118905564612</v>
       </c>
       <c r="E49" t="s">
         <v>120</v>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>0.5439404379758324</v>
+        <v>0.5425118905564612</v>
       </c>
       <c r="E50" t="s">
         <v>149</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>0.5439404379758324</v>
+        <v>0.5425118905564612</v>
       </c>
       <c r="E51" t="s">
         <v>151</v>
@@ -2144,7 +2144,7 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>0.5439404379758324</v>
+        <v>0.5425118905564612</v>
       </c>
       <c r="E52" t="s">
         <v>153</v>
@@ -2161,7 +2161,7 @@
         <v>11</v>
       </c>
       <c r="D53">
-        <v>0.5603939429589418</v>
+        <v>0.5586292667350129</v>
       </c>
       <c r="E53" t="s">
         <v>122</v>
@@ -2178,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="D54">
-        <v>0.5748474815549318</v>
+        <v>0.572746676526445</v>
       </c>
       <c r="E54" t="s">
         <v>122</v>
@@ -2195,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="D55">
-        <v>0.5748474815549318</v>
+        <v>0.572746676526445</v>
       </c>
       <c r="E55" t="s">
         <v>157</v>
@@ -2212,7 +2212,7 @@
         <v>13</v>
       </c>
       <c r="D56">
-        <v>0.5835868304734374</v>
+        <v>0.581418799684039</v>
       </c>
       <c r="E56" t="s">
         <v>122</v>
@@ -2229,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>0.5897043747163914</v>
+        <v>0.5868136669971933</v>
       </c>
       <c r="E57" t="s">
         <v>160</v>
@@ -2246,7 +2246,7 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.5897043747163914</v>
+        <v>0.5868136669971933</v>
       </c>
       <c r="E58" t="s">
         <v>153</v>
@@ -2263,7 +2263,7 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>0.6019898825229828</v>
+        <v>0.6001243676576864</v>
       </c>
       <c r="E59" t="s">
         <v>163</v>
@@ -2286,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="D60">
-        <v>0.6043259777146602</v>
+        <v>0.6025108821700476</v>
       </c>
       <c r="E60" t="s">
         <v>163</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="D61">
-        <v>0.6105611670392094</v>
+        <v>0.6085107813314062</v>
       </c>
       <c r="E61" t="s">
         <v>168</v>
@@ -2332,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="D62">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="D69">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="D78">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="D80">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="D104">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="D112">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="D114">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.6119561015781247</v>
+        <v>0.6099393287507773</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -40,13 +40,13 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1164,E1950,E1954,E1951,E1955,E422</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+    <t>E2263,E2398,E2266,E2153,E2356,E2457,E1118,E1164,E2141,E2504,E2671,E2142,E1036,E2274,E1176,E1037,E2275,E2394,E1163,E1950,E1954,E1951,E1955,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,andrstndn/C00280,CE2186/CE2183/C05302/C05284/C05290/C05140,C05476,C05472,C05488/C05497/C05477/C02140,C05487/C05475/C05478,C03917/C05293/C00523/C04373/C04295,CE2211/C05480,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C04042/C01953/C03681,C00410,C02538,C04042/C01953/C03681,C00410,C18038/C05138/C04518/C05485,C05487/C05475/C05478,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Tetrahydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$Estrone 3-sulfate$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
@@ -112,13 +112,13 @@
     <t>Omega-3 fatty acid metabolism</t>
   </si>
   <si>
-    <t>E2325,E92,E2326</t>
-  </si>
-  <si>
-    <t>C16300,C06426/C06427,C16300</t>
-  </si>
-  <si>
-    <t>Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid</t>
+    <t>E92,E2326,E2325</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C16300,C16300</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid</t>
   </si>
   <si>
     <t>CoA Catabolism</t>
@@ -301,13 +301,13 @@
     <t>Tyrosine metabolism</t>
   </si>
   <si>
-    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E283,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E833,E66,E410,E170</t>
-  </si>
-  <si>
-    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C03758,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Dopamine$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
+    <t>E918,E411,E144,E1438,E190,E908,E20,E413,E909,E159,E432,E1222,E287,E22,E288,E335,E632,E912,E40,E12,E290,E898,E914,E178,E291,E179,E338,E281,E1439,E8,E283,E833,E66,E410,E170</t>
+  </si>
+  <si>
+    <t>CE2176,C05589/C00788,CE5536,C05642,C09642,C00079/CE2172,C00822/C05604,C05589/C00788,C00079/CE2172,C00355,C05580,,C03758,C00822/C05604,C00082/CE2174,C05583/C05582,CE1918,C00079/CE2172,C05577/C01161,,C00082/CE2174,C05581,CE2176,C16586/CE2173,C00082/CE2174,C16586/CE2173,C05583/C05582,,C00268/C02953/C04244,,C03758,C02763/C00166,C05587/C07453,C05589/C00788,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Phenylalanine/$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$$Dopamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$5-hydroxytryptophol$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$L-Tyrosine/$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$L-Tyrosine/$2-Phenyl-1,3-propanediol monocarbamate/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$Dopamine$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine/Epinine; Deoxyepinephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
   </si>
   <si>
     <t>Carnitine shuttle</t>
@@ -1066,7 +1066,7 @@
         <v>62</v>
       </c>
       <c r="D2">
-        <v>0.002151224349170602</v>
+        <v>0.002319288751449555</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0.01909211609888909</v>
+        <v>0.01803331036453169</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1112,7 +1112,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.02317608107426766</v>
+        <v>0.02235256550310079</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1135,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>0.02974739920337473</v>
+        <v>0.02969697988269105</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1158,7 +1158,7 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>0.04136064940085041</v>
+        <v>0.04171358464563621</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.04537738861531739</v>
+        <v>0.04653703299104216</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>0.0482344834540596</v>
+        <v>0.04974706307457018</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>0.07604914203122637</v>
+        <v>0.07695668980353271</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>0.08233475067645922</v>
+        <v>0.08366245945446295</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.08325910488899346</v>
+        <v>0.08487252315087142</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>0.08517503907497354</v>
+        <v>0.0870573603804978</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1319,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.08914135896875683</v>
+        <v>0.0906875514697232</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1342,7 +1342,7 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>0.09154467992134586</v>
+        <v>0.09324213038436328</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1365,7 +1365,7 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>0.09189761516613167</v>
+        <v>0.09381354935211172</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1388,7 +1388,7 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.09189761516613167</v>
+        <v>0.09381354935211172</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1411,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1442496764760256</v>
+        <v>0.1469891262331726</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.1630560830910405</v>
+        <v>0.1653417589620343</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1630560830910405</v>
+        <v>0.1653417589620343</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.1747365590494278</v>
+        <v>0.1786020403018437</v>
       </c>
       <c r="E20" t="s">
         <v>71</v>
@@ -1497,7 +1497,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>0.1987361556948623</v>
+        <v>0.2021310566208971</v>
       </c>
       <c r="E21" t="s">
         <v>73</v>
@@ -1520,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>0.2302650375623939</v>
+        <v>0.2330381001999966</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.2302650375623939</v>
+        <v>0.2330381001999966</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
@@ -1566,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.2302650375623939</v>
+        <v>0.2330381001999966</v>
       </c>
       <c r="E24" t="s">
         <v>85</v>
@@ -1589,7 +1589,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2507857010806541</v>
+        <v>0.2534747315171174</v>
       </c>
       <c r="E25" t="s">
         <v>89</v>
@@ -1606,7 +1606,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.2903312549368918</v>
+        <v>0.2929866724928993</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -1629,7 +1629,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>0.2925328986067461</v>
+        <v>0.2957261222500462</v>
       </c>
       <c r="E27" t="s">
         <v>93</v>
@@ -1652,7 +1652,7 @@
         <v>152</v>
       </c>
       <c r="D28">
-        <v>0.3142804322616427</v>
+        <v>0.3167341725349154</v>
       </c>
       <c r="E28" t="s">
         <v>95</v>
@@ -1675,7 +1675,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.3208853632712055</v>
+        <v>0.3238937160719988</v>
       </c>
       <c r="E29" t="s">
         <v>99</v>
@@ -1698,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>0.3288684223794558</v>
+        <v>0.3325490327893649</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>0.3288684223794558</v>
+        <v>0.3325490327893649</v>
       </c>
       <c r="E31" t="s">
         <v>105</v>
@@ -1744,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>0.3288684223794558</v>
+        <v>0.3325490327893649</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>0.3622123997916001</v>
+        <v>0.367203912539285</v>
       </c>
       <c r="E33" t="s">
         <v>108</v>
@@ -1790,7 +1790,7 @@
         <v>43</v>
       </c>
       <c r="D34">
-        <v>0.3653888169946723</v>
+        <v>0.3704139426228131</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -1813,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>0.3728676828960858</v>
+        <v>0.3772205509151107</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
@@ -1830,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>0.4008672123157594</v>
+        <v>0.4056570477807095</v>
       </c>
       <c r="E36" t="s">
         <v>118</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>0.4251357120048402</v>
+        <v>0.4289507739365725</v>
       </c>
       <c r="E37" t="s">
         <v>120</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>0.4251357120048402</v>
+        <v>0.4289507739365725</v>
       </c>
       <c r="E38" t="s">
         <v>122</v>
@@ -1887,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>0.4251357120048402</v>
+        <v>0.4289507739365725</v>
       </c>
       <c r="E39" t="s">
         <v>124</v>
@@ -1904,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="D40">
-        <v>0.4276566780390246</v>
+        <v>0.432732222987849</v>
       </c>
       <c r="E40" t="s">
         <v>126</v>
@@ -1927,7 +1927,7 @@
         <v>120</v>
       </c>
       <c r="D41">
-        <v>0.4449168921530731</v>
+        <v>0.4485638896825264</v>
       </c>
       <c r="E41" t="s">
         <v>128</v>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>0.4674375220584528</v>
+        <v>0.4696895850489908</v>
       </c>
       <c r="E42" t="s">
         <v>122</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>0.4674375220584528</v>
+        <v>0.4696895850489908</v>
       </c>
       <c r="E43" t="s">
         <v>133</v>
@@ -1984,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>0.4969664375388649</v>
+        <v>0.4987647266432497</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
@@ -2007,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="D45">
-        <v>0.4969664375388649</v>
+        <v>0.4987647266432497</v>
       </c>
       <c r="E45" t="s">
         <v>137</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <v>0.5015209828406245</v>
+        <v>0.503857078032302</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -2053,7 +2053,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>0.517991294263962</v>
+        <v>0.5197055511672073</v>
       </c>
       <c r="E47" t="s">
         <v>143</v>
@@ -2076,7 +2076,7 @@
         <v>9</v>
       </c>
       <c r="D48">
-        <v>0.5254197408446917</v>
+        <v>0.5269491269054302</v>
       </c>
       <c r="E48" t="s">
         <v>122</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>0.5425118905564612</v>
+        <v>0.5448143728676829</v>
       </c>
       <c r="E49" t="s">
         <v>120</v>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>0.5425118905564612</v>
+        <v>0.5448143728676829</v>
       </c>
       <c r="E50" t="s">
         <v>149</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>0.5425118905564612</v>
+        <v>0.5448143728676829</v>
       </c>
       <c r="E51" t="s">
         <v>151</v>
@@ -2144,7 +2144,7 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>0.5425118905564612</v>
+        <v>0.5448143728676829</v>
       </c>
       <c r="E52" t="s">
         <v>153</v>
@@ -2161,7 +2161,7 @@
         <v>11</v>
       </c>
       <c r="D53">
-        <v>0.5586292667350129</v>
+        <v>0.5608309104048671</v>
       </c>
       <c r="E53" t="s">
         <v>122</v>
@@ -2178,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="D54">
-        <v>0.572746676526445</v>
+        <v>0.5748979008756155</v>
       </c>
       <c r="E54" t="s">
         <v>122</v>
@@ -2195,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="D55">
-        <v>0.572746676526445</v>
+        <v>0.5748979008756155</v>
       </c>
       <c r="E55" t="s">
         <v>157</v>
@@ -2212,7 +2212,7 @@
         <v>13</v>
       </c>
       <c r="D56">
-        <v>0.581418799684039</v>
+        <v>0.5836036369136653</v>
       </c>
       <c r="E56" t="s">
         <v>122</v>
@@ -2229,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>0.5868136669971933</v>
+        <v>0.5897379875968471</v>
       </c>
       <c r="E57" t="s">
         <v>160</v>
@@ -2246,7 +2246,7 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.5868136669971933</v>
+        <v>0.5897379875968471</v>
       </c>
       <c r="E58" t="s">
         <v>153</v>
@@ -2263,7 +2263,7 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>0.6001243676576864</v>
+        <v>0.6020739147241223</v>
       </c>
       <c r="E59" t="s">
         <v>163</v>
@@ -2286,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="D60">
-        <v>0.6025108821700476</v>
+        <v>0.6040738811112418</v>
       </c>
       <c r="E60" t="s">
         <v>163</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="D61">
-        <v>0.6085107813314062</v>
+        <v>0.6101578124737399</v>
       </c>
       <c r="E61" t="s">
         <v>168</v>
@@ -2332,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="D62">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="D69">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="D78">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="D80">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="D104">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="D112">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="D114">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="D119">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.6099393287507773</v>
+        <v>0.6113006504092369</v>
       </c>
     </row>
   </sheetData>
